--- a/results/link-prediction-gcn/Link/1shot/IMDB-BINARY/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/IMDB-BINARY/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4817±0.0000</t>
+          <t>0.4815±0.0002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5247±0.0010</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5366±0.0044</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5180±0.0000</t>
+          <t>0.5614±0.0052</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4817±0.0000</t>
+          <t>0.4815±0.0002</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5230±0.0038</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5294±0.0066</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5155±0.0000</t>
+          <t>0.5502±0.0284</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4817±0.0000</t>
+          <t>0.4815±0.0002</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5244±0.0015</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5184±0.0000</t>
+          <t>0.5315±0.0057</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5188±0.0003</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0004</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5293±0.0109</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5187±0.0004</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4817±0.0000</t>
+          <t>0.5515±0.0144</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5189±0.0006</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5181±0.0000</t>
+          <t>0.5178±0.0010</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5051±0.0000</t>
+          <t>0.5040±0.0104</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4999±0.0000</t>
+          <t>0.5085±0.0070</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5134±0.0000</t>
+          <t>0.5171±0.0025</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.5096±0.0065</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.5096±0.0065</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5001±0.0000</t>
+          <t>0.5096±0.0065</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5221±0.0000</t>
+          <t>0.5128±0.0080</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5956±0.0128</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5173±0.0000</t>
+          <t>0.5188±0.0005</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4817±0.0000</t>
+          <t>0.4815±0.0002</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5234±0.0071</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5452±0.0000</t>
+          <t>0.5920±0.0097</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5158±0.0000</t>
+          <t>0.5148±0.0035</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4817±0.0000</t>
+          <t>0.4815±0.0002</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5214±0.0010</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5221±0.0023</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5187±0.0001</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5188±0.0001</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0002</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5378±0.0170</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5188±0.0005</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4860±0.0000</t>
+          <t>0.4815±0.0002</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5195±0.0012</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5184±0.0000</t>
+          <t>0.5156±0.0019</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5141±0.0063</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5185±0.0002</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5186±0.0003</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5169±0.0021</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5169±0.0021</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5182±0.0000</t>
+          <t>0.5169±0.0021</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5185±0.0001</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.5734±0.0286</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5183±0.0000</t>
+          <t>0.5187±0.0002</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6832±0.0028</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6866±0.0003</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0001</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6824±0.0000</t>
+          <t>0.6879±0.0021</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6839±0.0024</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6841±0.0010</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6745±0.0000</t>
+          <t>0.6858±0.0069</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,322 +1490,322 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6836±0.0025</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6860±0.0020</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0003</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6827±0.0003</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6792±0.0023</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0003</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>0.2660±0.0494</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0002</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6818±0.0014</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6681±0.0106</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6726±0.0073</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6815±0.0024</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0066</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0066</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0066</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.6777±0.0074</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7052±0.0056</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.6825±0.0002</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6826±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6709±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6661±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6783±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.6663±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.6663±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.6663±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.6842±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7066±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.6816±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6814±0.0020</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6955±0.0024</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6787±0.0042</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6793±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6835±0.0010</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6834±0.0003</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0001</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0001</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6829±0.0002</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0002</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0002</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0002</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0002</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6823±0.0032</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6830±0.0003</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6827±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0164±0.0000</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0006</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6828±0.0000</t>
+          <t>0.6802±0.0018</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6784±0.0063</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6828±0.0002</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0002</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6813±0.0019</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6813±0.0019</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6813±0.0019</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6829±0.0001</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7107±0.0000</t>
+          <t>0.7028±0.0102</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6830±0.0002</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3356±0.0000</t>
+          <t>0.3300±0.0064</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7228±0.0000</t>
+          <t>0.7295±0.0033</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6799±0.0000</t>
+          <t>0.7064±0.0025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.7029±0.0000</t>
+          <t>0.6884±0.0038</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7363±0.0044</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7340±0.0036</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7233±0.0000</t>
+          <t>0.7320±0.0038</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7330±0.0030</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7330±0.0030</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7330±0.0030</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.7362±0.0030</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.7211±0.0000</t>
+          <t>0.7319±0.0015</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7200±0.0000</t>
+          <t>0.7428±0.0055</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.3357±0.0000</t>
+          <t>0.3299±0.0064</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7226±0.0000</t>
+          <t>0.7285±0.0025</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.7216±0.0082</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.7003±0.0000</t>
+          <t>0.7100±0.0294</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.7447±0.0054</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.7458±0.0026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7322±0.0022</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.7459±0.0014</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.7459±0.0014</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7264±0.0000</t>
+          <t>0.7459±0.0014</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7233±0.0000</t>
+          <t>0.7321±0.0011</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7285±0.0000</t>
+          <t>0.7234±0.0110</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7475±0.0088</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.3358±0.0000</t>
+          <t>0.3309±0.0065</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7229±0.0000</t>
+          <t>0.7283±0.0028</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6541±0.0000</t>
+          <t>0.7192±0.0157</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7018±0.0000</t>
+          <t>0.7210±0.0329</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7540±0.0054</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7573±0.0012</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7321±0.0029</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7610±0.0004</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7610±0.0004</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7610±0.0004</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.7230±0.0000</t>
+          <t>0.7320±0.0018</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7084±0.0000</t>
+          <t>0.7242±0.0063</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7189±0.0000</t>
+          <t>0.7629±0.0019</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6907±0.0000</t>
+          <t>0.7141±0.0180</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7339±0.0000</t>
+          <t>0.7230±0.0032</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.6862±0.0000</t>
+          <t>0.7113±0.0280</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.7057±0.0000</t>
+          <t>0.7256±0.0196</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.7185±0.0000</t>
+          <t>0.7205±0.0010</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.7294±0.0107</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.7065±0.0000</t>
+          <t>0.7271±0.0136</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7262±0.0071</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7262±0.0071</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7262±0.0071</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7173±0.0000</t>
+          <t>0.7232±0.0066</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7587±0.0000</t>
+          <t>0.7509±0.0012</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7247±0.0000</t>
+          <t>0.7426±0.0049</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.3358±0.0000</t>
+          <t>0.3307±0.0066</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7278±0.0020</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.7338±0.0000</t>
+          <t>0.7652±0.0084</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.7122±0.0000</t>
+          <t>0.7478±0.0075</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7284±0.0019</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7286±0.0023</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.7243±0.0000</t>
+          <t>0.7285±0.0017</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7291±0.0020</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7291±0.0020</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7291±0.0020</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7290±0.0021</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7199±0.0000</t>
+          <t>0.7276±0.0012</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7204±0.0000</t>
+          <t>0.7322±0.0078</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.3358±0.0000</t>
+          <t>0.3310±0.0066</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7227±0.0000</t>
+          <t>0.7284±0.0022</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6533±0.0000</t>
+          <t>0.7126±0.0121</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6937±0.0000</t>
+          <t>0.7242±0.0080</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7227±0.0000</t>
+          <t>0.7441±0.0098</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7228±0.0000</t>
+          <t>0.7485±0.0027</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.7231±0.0000</t>
+          <t>0.7321±0.0030</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7227±0.0000</t>
+          <t>0.7491±0.0046</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7227±0.0000</t>
+          <t>0.7491±0.0046</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7227±0.0000</t>
+          <t>0.7491±0.0046</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.7231±0.0000</t>
+          <t>0.7331±0.0021</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6873±0.0000</t>
+          <t>0.7236±0.0065</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7561±0.0066</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7122±0.0000</t>
+          <t>0.7149±0.0054</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7154±0.0000</t>
+          <t>0.7306±0.0015</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.7058±0.0179</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.7198±0.0000</t>
+          <t>0.7071±0.0033</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7369±0.0000</t>
+          <t>0.7318±0.0090</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.7419±0.0000</t>
+          <t>0.7368±0.0008</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7113±0.0000</t>
+          <t>0.7237±0.0143</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7371±0.0000</t>
+          <t>0.7368±0.0008</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7371±0.0000</t>
+          <t>0.7368±0.0008</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7371±0.0000</t>
+          <t>0.7368±0.0008</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7035±0.0000</t>
+          <t>0.7249±0.0032</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7722±0.0000</t>
+          <t>0.7683±0.0032</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7549±0.0000</t>
+          <t>0.7636±0.0023</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4441±0.0000</t>
+          <t>0.4406±0.0076</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7435±0.0000</t>
+          <t>0.7430±0.0076</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6554±0.0000</t>
+          <t>0.7349±0.0118</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7248±0.0000</t>
+          <t>0.7209±0.0038</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7452±0.0000</t>
+          <t>0.7533±0.0016</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7447±0.0000</t>
+          <t>0.7518±0.0027</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7451±0.0000</t>
+          <t>0.7511±0.0025</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7509±0.0031</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7509±0.0031</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7448±0.0000</t>
+          <t>0.7509±0.0031</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7445±0.0000</t>
+          <t>0.7539±0.0028</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.7279±0.0023</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7391±0.0000</t>
+          <t>0.7504±0.0028</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4443±0.0000</t>
+          <t>0.4405±0.0077</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7429±0.0000</t>
+          <t>0.7491±0.0033</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6673±0.0000</t>
+          <t>0.7410±0.0148</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7236±0.0000</t>
+          <t>0.7356±0.0237</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7492±0.0000</t>
+          <t>0.7543±0.0011</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7491±0.0000</t>
+          <t>0.7537±0.0025</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7504±0.0017</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7492±0.0000</t>
+          <t>0.7539±0.0013</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7492±0.0000</t>
+          <t>0.7539±0.0013</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7492±0.0000</t>
+          <t>0.7539±0.0013</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7441±0.0000</t>
+          <t>0.7501±0.0010</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7292±0.0000</t>
+          <t>0.7236±0.0090</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7393±0.0000</t>
+          <t>0.7513±0.0042</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.4445±0.0000</t>
+          <t>0.4422±0.0077</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7447±0.0000</t>
+          <t>0.7519±0.0014</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6332±0.0000</t>
+          <t>0.7417±0.0135</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7027±0.0000</t>
+          <t>0.7423±0.0209</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7458±0.0000</t>
+          <t>0.7614±0.0037</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7629±0.0009</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7455±0.0000</t>
+          <t>0.7510±0.0023</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7653±0.0019</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7653±0.0019</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7653±0.0019</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7452±0.0000</t>
+          <t>0.7501±0.0021</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7123±0.0000</t>
+          <t>0.7220±0.0050</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7392±0.0000</t>
+          <t>0.7593±0.0014</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7363±0.0062</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7453±0.0000</t>
+          <t>0.7477±0.0025</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6717±0.0000</t>
+          <t>0.7437±0.0169</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7319±0.0000</t>
+          <t>0.7462±0.0101</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.7489±0.0000</t>
+          <t>0.7528±0.0032</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7474±0.0000</t>
+          <t>0.7550±0.0069</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7395±0.0000</t>
+          <t>0.7550±0.0081</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7485±0.0000</t>
+          <t>0.7533±0.0053</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7485±0.0000</t>
+          <t>0.7533±0.0053</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7485±0.0000</t>
+          <t>0.7533±0.0053</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7518±0.0000</t>
+          <t>0.7551±0.0026</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7489±0.0000</t>
+          <t>0.7421±0.0013</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7425±0.0000</t>
+          <t>0.7563±0.0027</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.4446±0.0000</t>
+          <t>0.4420±0.0078</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7473±0.0006</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.7384±0.0000</t>
+          <t>0.7869±0.0068</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7341±0.0000</t>
+          <t>0.7652±0.0091</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7495±0.0025</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7494±0.0030</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7482±0.0000</t>
+          <t>0.7499±0.0018</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7471±0.0000</t>
+          <t>0.7504±0.0026</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7471±0.0000</t>
+          <t>0.7504±0.0026</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7471±0.0000</t>
+          <t>0.7504±0.0026</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7479±0.0000</t>
+          <t>0.7510±0.0027</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7200±0.0000</t>
+          <t>0.7295±0.0002</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7386±0.0000</t>
+          <t>0.7494±0.0094</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.4445±0.0000</t>
+          <t>0.4424±0.0078</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7432±0.0000</t>
+          <t>0.7497±0.0023</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6294±0.0000</t>
+          <t>0.7359±0.0137</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6920±0.0000</t>
+          <t>0.7482±0.0075</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7395±0.0000</t>
+          <t>0.7571±0.0036</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7402±0.0000</t>
+          <t>0.7587±0.0034</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7453±0.0000</t>
+          <t>0.7513±0.0028</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7397±0.0000</t>
+          <t>0.7594±0.0027</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7397±0.0000</t>
+          <t>0.7594±0.0027</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7397±0.0000</t>
+          <t>0.7593±0.0027</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7437±0.0000</t>
+          <t>0.7512±0.0019</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6959±0.0000</t>
+          <t>0.7208±0.0039</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7343±0.0000</t>
+          <t>0.7570±0.0030</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7316±0.0000</t>
+          <t>0.7364±0.0011</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7485±0.0000</t>
+          <t>0.7482±0.0005</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6492±0.0000</t>
+          <t>0.7378±0.0124</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7418±0.0000</t>
+          <t>0.7349±0.0028</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7531±0.0000</t>
+          <t>0.7565±0.0081</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7554±0.0000</t>
+          <t>0.7602±0.0015</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7533±0.0000</t>
+          <t>0.7510±0.0045</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7534±0.0000</t>
+          <t>0.7624±0.0012</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7534±0.0000</t>
+          <t>0.7624±0.0012</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7534±0.0000</t>
+          <t>0.7624±0.0012</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7526±0.0000</t>
+          <t>0.7489±0.0019</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7547±0.0000</t>
+          <t>0.7493±0.0043</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7545±0.0000</t>
+          <t>0.7644±0.0026</t>
         </is>
       </c>
     </row>
